--- a/New_CenterOfRotation/Finite_COR/Data Files/C34_Data/Y_Z Data Model 3-C34.xlsx
+++ b/New_CenterOfRotation/Finite_COR/Data Files/C34_Data/Y_Z Data Model 3-C34.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="14">
   <si>
     <t>Descriptions are [X,Y,Z] coords in the model. If a node is in the middle on the right, and top of C4, it would be [1,0,1] C4. Bottom would be [1,0,-1] C4</t>
   </si>
@@ -62,16 +62,13 @@
   <si>
     <t>Z (U3)</t>
   </si>
-  <si>
-    <t/>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
   <numFmts count="0"/>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -82,6 +79,12 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -119,6 +122,13 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FFc6c6c6"/>
       </left>
@@ -133,53 +143,46 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="17">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="3" applyFill="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="3" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
@@ -189,12 +192,9 @@
       <alignment horizontal="right"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="3" applyFill="1" quotePrefix="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -798,10 +798,10 @@
       <c r="I6" s="7">
         <v>0</v>
       </c>
-      <c r="J6" s="17">
+      <c r="J6" s="16">
         <v>1.98781</v>
       </c>
-      <c r="K6" s="17">
+      <c r="K6" s="16">
         <v>-1.26085</v>
       </c>
       <c r="L6" s="9"/>
@@ -859,10 +859,10 @@
       <c r="I7" s="11">
         <v>0.05</v>
       </c>
-      <c r="J7" s="17">
+      <c r="J7" s="16">
         <v>1.97641</v>
       </c>
-      <c r="K7" s="17">
+      <c r="K7" s="16">
         <v>-1.25743</v>
       </c>
       <c r="L7" s="9"/>
@@ -920,10 +920,10 @@
       <c r="I8" s="11">
         <v>0.1</v>
       </c>
-      <c r="J8" s="17">
+      <c r="J8" s="16">
         <v>2.0847</v>
       </c>
-      <c r="K8" s="17">
+      <c r="K8" s="16">
         <v>-1.25824</v>
       </c>
       <c r="L8" s="9"/>
@@ -981,10 +981,10 @@
       <c r="I9" s="11">
         <v>0.15</v>
       </c>
-      <c r="J9" s="17">
+      <c r="J9" s="16">
         <v>2.2406</v>
       </c>
-      <c r="K9" s="17">
+      <c r="K9" s="16">
         <v>-1.27163</v>
       </c>
       <c r="L9" s="9"/>
@@ -994,7 +994,7 @@
       <c r="N9" s="11">
         <v>1.42312</v>
       </c>
-      <c r="O9" s="17">
+      <c r="O9" s="16">
         <v>-0.390673</v>
       </c>
       <c r="P9" s="9"/>
@@ -1042,10 +1042,10 @@
       <c r="I10" s="11">
         <v>0.2</v>
       </c>
-      <c r="J10" s="17">
+      <c r="J10" s="16">
         <v>2.37906</v>
       </c>
-      <c r="K10" s="17">
+      <c r="K10" s="16">
         <v>-1.28657</v>
       </c>
       <c r="L10" s="9"/>
@@ -1103,10 +1103,10 @@
       <c r="I11" s="11">
         <v>0.25</v>
       </c>
-      <c r="J11" s="17">
+      <c r="J11" s="16">
         <v>2.58841</v>
       </c>
-      <c r="K11" s="17">
+      <c r="K11" s="16">
         <v>-1.31218</v>
       </c>
       <c r="L11" s="9"/>
@@ -1164,10 +1164,10 @@
       <c r="I12" s="11">
         <v>0.30198</v>
       </c>
-      <c r="J12" s="17">
+      <c r="J12" s="16">
         <v>2.85645</v>
       </c>
-      <c r="K12" s="17">
+      <c r="K12" s="16">
         <v>-1.34763</v>
       </c>
       <c r="L12" s="9"/>
@@ -1225,10 +1225,10 @@
       <c r="I13" s="11">
         <v>0.35365</v>
       </c>
-      <c r="J13" s="17">
+      <c r="J13" s="16">
         <v>3.1376</v>
       </c>
-      <c r="K13" s="17">
+      <c r="K13" s="16">
         <v>-1.38986</v>
       </c>
       <c r="L13" s="9"/>
@@ -1286,10 +1286,10 @@
       <c r="I14" s="11">
         <v>0.40358</v>
       </c>
-      <c r="J14" s="17">
+      <c r="J14" s="16">
         <v>3.46702</v>
       </c>
-      <c r="K14" s="17">
+      <c r="K14" s="16">
         <v>-1.4398</v>
       </c>
       <c r="L14" s="9"/>
@@ -1347,10 +1347,10 @@
       <c r="I15" s="11">
         <v>0.45421</v>
       </c>
-      <c r="J15" s="17">
+      <c r="J15" s="16">
         <v>3.88637</v>
       </c>
-      <c r="K15" s="17">
+      <c r="K15" s="16">
         <v>-1.50577</v>
       </c>
       <c r="L15" s="9"/>
@@ -1408,10 +1408,10 @@
       <c r="I16" s="11">
         <v>0.50322</v>
       </c>
-      <c r="J16" s="17">
+      <c r="J16" s="16">
         <v>4.29052</v>
       </c>
-      <c r="K16" s="17">
+      <c r="K16" s="16">
         <v>-1.57359</v>
       </c>
       <c r="L16" s="9"/>
@@ -1469,10 +1469,10 @@
       <c r="I17" s="11">
         <v>0.55384</v>
       </c>
-      <c r="J17" s="17">
+      <c r="J17" s="16">
         <v>4.79779</v>
       </c>
-      <c r="K17" s="17">
+      <c r="K17" s="16">
         <v>-1.6644</v>
       </c>
       <c r="L17" s="9"/>
@@ -1530,10 +1530,10 @@
       <c r="I18" s="11">
         <v>0.60384</v>
       </c>
-      <c r="J18" s="17">
+      <c r="J18" s="16">
         <v>5.24103</v>
       </c>
-      <c r="K18" s="17">
+      <c r="K18" s="16">
         <v>-1.74837</v>
       </c>
       <c r="L18" s="9"/>
@@ -1591,10 +1591,10 @@
       <c r="I19" s="11">
         <v>0.65565</v>
       </c>
-      <c r="J19" s="17">
+      <c r="J19" s="16">
         <v>5.73504</v>
       </c>
-      <c r="K19" s="17">
+      <c r="K19" s="16">
         <v>-1.84125</v>
       </c>
       <c r="L19" s="9"/>
@@ -1652,10 +1652,10 @@
       <c r="I20" s="11">
         <v>0.70225</v>
       </c>
-      <c r="J20" s="17">
+      <c r="J20" s="16">
         <v>6.29713</v>
       </c>
-      <c r="K20" s="17">
+      <c r="K20" s="16">
         <v>-1.94778</v>
       </c>
       <c r="L20" s="9"/>
@@ -1713,10 +1713,10 @@
       <c r="I21" s="11">
         <v>0.75206</v>
       </c>
-      <c r="J21" s="17">
+      <c r="J21" s="16">
         <v>6.93639</v>
       </c>
-      <c r="K21" s="17">
+      <c r="K21" s="16">
         <v>-2.07858</v>
       </c>
       <c r="L21" s="9"/>
@@ -1774,10 +1774,10 @@
       <c r="I22" s="11">
         <v>0.80139</v>
       </c>
-      <c r="J22" s="17">
+      <c r="J22" s="16">
         <v>7.52864</v>
       </c>
-      <c r="K22" s="17">
+      <c r="K22" s="16">
         <v>-2.209</v>
       </c>
       <c r="L22" s="9"/>
@@ -1835,10 +1835,10 @@
       <c r="I23" s="11">
         <v>0.85108</v>
       </c>
-      <c r="J23" s="17">
+      <c r="J23" s="16">
         <v>8.15969</v>
       </c>
-      <c r="K23" s="17">
+      <c r="K23" s="16">
         <v>-2.35833</v>
       </c>
       <c r="L23" s="9"/>
@@ -1896,10 +1896,10 @@
       <c r="I24" s="11">
         <v>0.90339</v>
       </c>
-      <c r="J24" s="17">
+      <c r="J24" s="16">
         <v>8.94546</v>
       </c>
-      <c r="K24" s="17">
+      <c r="K24" s="16">
         <v>-2.55901</v>
       </c>
       <c r="L24" s="9"/>
@@ -1957,10 +1957,10 @@
       <c r="I25" s="11">
         <v>0.95085</v>
       </c>
-      <c r="J25" s="17">
+      <c r="J25" s="16">
         <v>9.65863</v>
       </c>
-      <c r="K25" s="17">
+      <c r="K25" s="16">
         <v>-2.75556</v>
       </c>
       <c r="L25" s="9"/>
@@ -2018,10 +2018,10 @@
       <c r="I26" s="7">
         <v>1</v>
       </c>
-      <c r="J26" s="17">
+      <c r="J26" s="16">
         <v>10.2011</v>
       </c>
-      <c r="K26" s="17">
+      <c r="K26" s="16">
         <v>-2.91422</v>
       </c>
       <c r="L26" s="9"/>
@@ -2377,7 +2377,7 @@
       <c r="N6" s="11">
         <v>1.42966</v>
       </c>
-      <c r="O6" s="17">
+      <c r="O6" s="16">
         <v>-0.49437</v>
       </c>
       <c r="P6" s="9"/>
@@ -2438,7 +2438,7 @@
       <c r="N7" s="11">
         <v>1.36793</v>
       </c>
-      <c r="O7" s="17">
+      <c r="O7" s="16">
         <v>-0.543391</v>
       </c>
       <c r="P7" s="9"/>
@@ -2499,7 +2499,7 @@
       <c r="N8" s="11">
         <v>1.23178</v>
       </c>
-      <c r="O8" s="17">
+      <c r="O8" s="16">
         <v>-0.63976</v>
       </c>
       <c r="P8" s="9"/>
@@ -2560,7 +2560,7 @@
       <c r="N9" s="11">
         <v>1.08227</v>
       </c>
-      <c r="O9" s="17">
+      <c r="O9" s="16">
         <v>-0.736495</v>
       </c>
       <c r="P9" s="9"/>
@@ -2621,7 +2621,7 @@
       <c r="N10" s="11">
         <v>0.878132</v>
       </c>
-      <c r="O10" s="17">
+      <c r="O10" s="16">
         <v>-0.848519</v>
       </c>
       <c r="P10" s="9"/>
@@ -2682,7 +2682,7 @@
       <c r="N11" s="11">
         <v>0.696042</v>
       </c>
-      <c r="O11" s="17">
+      <c r="O11" s="16">
         <v>-0.93231</v>
       </c>
       <c r="P11" s="9"/>
@@ -2743,7 +2743,7 @@
       <c r="N12" s="11">
         <v>0.44829</v>
       </c>
-      <c r="O12" s="17">
+      <c r="O12" s="16">
         <v>-1.03999</v>
       </c>
       <c r="P12" s="9"/>
@@ -2804,7 +2804,7 @@
       <c r="N13" s="11">
         <v>0.176565</v>
       </c>
-      <c r="O13" s="17">
+      <c r="O13" s="16">
         <v>-1.15075</v>
       </c>
       <c r="P13" s="9"/>
@@ -2865,7 +2865,7 @@
       <c r="N14" s="11">
         <v>-0.17473</v>
       </c>
-      <c r="O14" s="17">
+      <c r="O14" s="16">
         <v>-1.28746</v>
       </c>
       <c r="P14" s="9"/>
@@ -2926,7 +2926,7 @@
       <c r="N15" s="11">
         <v>-0.343515</v>
       </c>
-      <c r="O15" s="17">
+      <c r="O15" s="16">
         <v>-1.35157</v>
       </c>
       <c r="P15" s="9"/>
@@ -2987,7 +2987,7 @@
       <c r="N16" s="11">
         <v>-0.759319</v>
       </c>
-      <c r="O16" s="17">
+      <c r="O16" s="16">
         <v>-1.50628</v>
       </c>
       <c r="P16" s="9"/>
@@ -3048,7 +3048,7 @@
       <c r="N17" s="11">
         <v>-1.2109</v>
       </c>
-      <c r="O17" s="17">
+      <c r="O17" s="16">
         <v>-1.67399</v>
       </c>
       <c r="P17" s="9"/>
@@ -3109,7 +3109,7 @@
       <c r="N18" s="11">
         <v>-1.61971</v>
       </c>
-      <c r="O18" s="17">
+      <c r="O18" s="16">
         <v>-1.82594</v>
       </c>
       <c r="P18" s="9"/>
@@ -3170,7 +3170,7 @@
       <c r="N19" s="11">
         <v>-1.92697</v>
       </c>
-      <c r="O19" s="17">
+      <c r="O19" s="16">
         <v>-1.94114</v>
       </c>
       <c r="P19" s="9"/>
@@ -3231,7 +3231,7 @@
       <c r="N20" s="11">
         <v>-2.34565</v>
       </c>
-      <c r="O20" s="17">
+      <c r="O20" s="16">
         <v>-2.10212</v>
       </c>
       <c r="P20" s="9"/>
@@ -3292,7 +3292,7 @@
       <c r="N21" s="11">
         <v>-2.89858</v>
       </c>
-      <c r="O21" s="17">
+      <c r="O21" s="16">
         <v>-2.32476</v>
       </c>
       <c r="P21" s="9"/>
@@ -3353,7 +3353,7 @@
       <c r="N22" s="11">
         <v>-3.25189</v>
       </c>
-      <c r="O22" s="17">
+      <c r="O22" s="16">
         <v>-2.47611</v>
       </c>
       <c r="P22" s="9"/>
@@ -3414,7 +3414,7 @@
       <c r="N23" s="11">
         <v>-3.72859</v>
       </c>
-      <c r="O23" s="17">
+      <c r="O23" s="16">
         <v>-2.68963</v>
       </c>
       <c r="P23" s="9"/>
@@ -3475,7 +3475,7 @@
       <c r="N24" s="11">
         <v>-4.25245</v>
       </c>
-      <c r="O24" s="17">
+      <c r="O24" s="16">
         <v>-2.93318</v>
       </c>
       <c r="P24" s="9"/>
@@ -3536,7 +3536,7 @@
       <c r="N25" s="11">
         <v>-4.79117</v>
       </c>
-      <c r="O25" s="17">
+      <c r="O25" s="16">
         <v>-3.19196</v>
       </c>
       <c r="P25" s="9"/>
@@ -3597,7 +3597,7 @@
       <c r="N26" s="11">
         <v>-5.17239</v>
       </c>
-      <c r="O26" s="17">
+      <c r="O26" s="16">
         <v>-3.37968</v>
       </c>
       <c r="P26" s="9"/>
@@ -3659,7 +3659,7 @@
     <col min="23" max="23" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="15">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3686,7 +3686,7 @@
       <c r="V1" s="2"/>
       <c r="W1" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
       <c r="A2" s="4" t="s">
         <v>1</v>
       </c>
@@ -3736,49 +3736,37 @@
       <c r="W2" s="5"/>
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
-      <c r="A3" s="16" t="s">
-        <v>14</v>
-      </c>
+      <c r="A3" s="6"/>
       <c r="B3" s="7">
         <v>11026</v>
       </c>
       <c r="C3" s="8"/>
       <c r="D3" s="9"/>
-      <c r="E3" s="16" t="s">
-        <v>14</v>
-      </c>
+      <c r="E3" s="6"/>
       <c r="F3" s="7">
         <v>13917</v>
       </c>
       <c r="G3" s="8"/>
       <c r="H3" s="9"/>
-      <c r="I3" s="16" t="s">
-        <v>14</v>
-      </c>
+      <c r="I3" s="6"/>
       <c r="J3" s="7">
         <v>9053</v>
       </c>
       <c r="K3" s="8"/>
       <c r="L3" s="9"/>
-      <c r="M3" s="16" t="s">
-        <v>14</v>
-      </c>
+      <c r="M3" s="6"/>
       <c r="N3" s="7">
         <v>27976</v>
       </c>
       <c r="O3" s="8"/>
       <c r="P3" s="9"/>
-      <c r="Q3" s="16" t="s">
-        <v>14</v>
-      </c>
+      <c r="Q3" s="6"/>
       <c r="R3" s="7">
         <v>25638</v>
       </c>
       <c r="S3" s="8"/>
       <c r="T3" s="9"/>
-      <c r="U3" s="16" t="s">
-        <v>14</v>
-      </c>
+      <c r="U3" s="6"/>
       <c r="V3" s="7">
         <v>31579</v>
       </c>
@@ -5302,9 +5290,7 @@
       <c r="W2" s="5"/>
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
-      <c r="A3" s="16" t="s">
-        <v>14</v>
-      </c>
+      <c r="A3" s="6"/>
       <c r="B3" s="7">
         <v>11026</v>
       </c>
@@ -5496,10 +5482,10 @@
       <c r="I6" s="7">
         <v>0</v>
       </c>
-      <c r="J6" s="17">
+      <c r="J6" s="16">
         <v>1.98781</v>
       </c>
-      <c r="K6" s="17">
+      <c r="K6" s="16">
         <v>-1.26085</v>
       </c>
       <c r="L6" s="9"/>
@@ -5557,10 +5543,10 @@
       <c r="I7" s="11">
         <v>0.05</v>
       </c>
-      <c r="J7" s="17">
+      <c r="J7" s="16">
         <v>1.93092</v>
       </c>
-      <c r="K7" s="17">
+      <c r="K7" s="16">
         <v>-1.23833</v>
       </c>
       <c r="L7" s="9"/>
@@ -5618,10 +5604,10 @@
       <c r="I8" s="11">
         <v>0.1</v>
       </c>
-      <c r="J8" s="17">
+      <c r="J8" s="16">
         <v>1.83789</v>
       </c>
-      <c r="K8" s="17">
+      <c r="K8" s="16">
         <v>-1.16783</v>
       </c>
       <c r="L8" s="9"/>
@@ -5679,10 +5665,10 @@
       <c r="I9" s="11">
         <v>0.15</v>
       </c>
-      <c r="J9" s="17">
+      <c r="J9" s="16">
         <v>1.73957</v>
       </c>
-      <c r="K9" s="17">
+      <c r="K9" s="16">
         <v>-1.08737</v>
       </c>
       <c r="L9" s="9"/>
@@ -5740,10 +5726,10 @@
       <c r="I10" s="11">
         <v>0.2</v>
       </c>
-      <c r="J10" s="17">
+      <c r="J10" s="16">
         <v>1.69321</v>
       </c>
-      <c r="K10" s="17">
+      <c r="K10" s="16">
         <v>-1.04857</v>
       </c>
       <c r="L10" s="9"/>
@@ -5801,10 +5787,10 @@
       <c r="I11" s="11">
         <v>0.25</v>
       </c>
-      <c r="J11" s="17">
+      <c r="J11" s="16">
         <v>1.58629</v>
       </c>
-      <c r="K11" s="17">
+      <c r="K11" s="16">
         <v>-0.959588</v>
       </c>
       <c r="L11" s="9"/>
@@ -5862,10 +5848,10 @@
       <c r="I12" s="11">
         <v>0.30198</v>
       </c>
-      <c r="J12" s="17">
+      <c r="J12" s="16">
         <v>1.50716</v>
       </c>
-      <c r="K12" s="17">
+      <c r="K12" s="16">
         <v>-0.894438</v>
       </c>
       <c r="L12" s="9"/>
@@ -5923,10 +5909,10 @@
       <c r="I13" s="11">
         <v>0.35365</v>
       </c>
-      <c r="J13" s="17">
+      <c r="J13" s="16">
         <v>1.42526</v>
       </c>
-      <c r="K13" s="17">
+      <c r="K13" s="16">
         <v>-0.828337</v>
       </c>
       <c r="L13" s="9"/>
@@ -5984,10 +5970,10 @@
       <c r="I14" s="11">
         <v>0.40358</v>
       </c>
-      <c r="J14" s="17">
+      <c r="J14" s="16">
         <v>1.33936</v>
       </c>
-      <c r="K14" s="17">
+      <c r="K14" s="16">
         <v>-0.757834</v>
       </c>
       <c r="L14" s="9"/>
@@ -6045,10 +6031,10 @@
       <c r="I15" s="11">
         <v>0.45421</v>
       </c>
-      <c r="J15" s="17">
+      <c r="J15" s="16">
         <v>1.28048</v>
       </c>
-      <c r="K15" s="17">
+      <c r="K15" s="16">
         <v>-0.706844</v>
       </c>
       <c r="L15" s="9"/>
@@ -6106,10 +6092,10 @@
       <c r="I16" s="11">
         <v>0.50322</v>
       </c>
-      <c r="J16" s="17">
+      <c r="J16" s="16">
         <v>1.22242</v>
       </c>
-      <c r="K16" s="17">
+      <c r="K16" s="16">
         <v>-0.651541</v>
       </c>
       <c r="L16" s="9"/>
@@ -6167,10 +6153,10 @@
       <c r="I17" s="11">
         <v>0.55384</v>
       </c>
-      <c r="J17" s="17">
+      <c r="J17" s="16">
         <v>1.19587</v>
       </c>
-      <c r="K17" s="17">
+      <c r="K17" s="16">
         <v>-0.619733</v>
       </c>
       <c r="L17" s="9"/>
@@ -6228,10 +6214,10 @@
       <c r="I18" s="11">
         <v>0.60384</v>
       </c>
-      <c r="J18" s="17">
+      <c r="J18" s="16">
         <v>1.17593</v>
       </c>
-      <c r="K18" s="17">
+      <c r="K18" s="16">
         <v>-0.587835</v>
       </c>
       <c r="L18" s="9"/>
@@ -6289,10 +6275,10 @@
       <c r="I19" s="11">
         <v>0.65565</v>
       </c>
-      <c r="J19" s="17">
+      <c r="J19" s="16">
         <v>1.16813</v>
       </c>
-      <c r="K19" s="17">
+      <c r="K19" s="16">
         <v>-0.557934</v>
       </c>
       <c r="L19" s="9"/>
@@ -6350,10 +6336,10 @@
       <c r="I20" s="11">
         <v>0.70225</v>
       </c>
-      <c r="J20" s="17">
+      <c r="J20" s="16">
         <v>1.17677</v>
       </c>
-      <c r="K20" s="17">
+      <c r="K20" s="16">
         <v>-0.536058</v>
       </c>
       <c r="L20" s="9"/>
@@ -6411,10 +6397,10 @@
       <c r="I21" s="11">
         <v>0.75206</v>
       </c>
-      <c r="J21" s="17">
+      <c r="J21" s="16">
         <v>1.20775</v>
       </c>
-      <c r="K21" s="17">
+      <c r="K21" s="16">
         <v>-0.517463</v>
       </c>
       <c r="L21" s="9"/>
@@ -6472,10 +6458,10 @@
       <c r="I22" s="11">
         <v>0.80139</v>
       </c>
-      <c r="J22" s="17">
+      <c r="J22" s="16">
         <v>1.24882</v>
       </c>
-      <c r="K22" s="17">
+      <c r="K22" s="16">
         <v>-0.507468</v>
       </c>
       <c r="L22" s="9"/>
@@ -6533,10 +6519,10 @@
       <c r="I23" s="11">
         <v>0.85108</v>
       </c>
-      <c r="J23" s="17">
+      <c r="J23" s="16">
         <v>1.31632</v>
       </c>
-      <c r="K23" s="17">
+      <c r="K23" s="16">
         <v>-0.502286</v>
       </c>
       <c r="L23" s="9"/>
@@ -6594,10 +6580,10 @@
       <c r="I24" s="11">
         <v>0.90339</v>
       </c>
-      <c r="J24" s="17">
+      <c r="J24" s="16">
         <v>1.43885</v>
       </c>
-      <c r="K24" s="17">
+      <c r="K24" s="16">
         <v>-0.505706</v>
       </c>
       <c r="L24" s="9"/>
@@ -6655,10 +6641,10 @@
       <c r="I25" s="11">
         <v>0.95085</v>
       </c>
-      <c r="J25" s="17">
+      <c r="J25" s="16">
         <v>1.48848</v>
       </c>
-      <c r="K25" s="17">
+      <c r="K25" s="16">
         <v>-0.50925</v>
       </c>
       <c r="L25" s="9"/>
@@ -6716,10 +6702,10 @@
       <c r="I26" s="7">
         <v>1</v>
       </c>
-      <c r="J26" s="17">
+      <c r="J26" s="16">
         <v>1.60794</v>
       </c>
-      <c r="K26" s="17">
+      <c r="K26" s="16">
         <v>-0.520958</v>
       </c>
       <c r="L26" s="9"/>
@@ -6763,1586 +6749,1559 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:X26"/>
+  <dimension ref="A1:W26"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="15" width="3.005" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="3" max="3" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="15" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="15" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="7" max="7" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="15" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="10" max="10" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="15" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="10" max="10" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="11" max="11" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="12" max="12" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="13" max="13" style="15" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="14" max="14" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="12" max="12" style="15" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="13" max="13" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="14" max="14" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="15" max="15" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="16" max="16" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="17" max="17" style="15" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="18" max="18" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="16" max="16" style="15" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="17" max="17" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="18" max="18" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="19" max="19" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="20" max="20" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="21" max="21" style="15" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="22" max="22" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="20" max="20" style="15" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="21" max="21" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="22" max="22" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="23" max="23" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="24" max="24" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="15">
-      <c r="A1" s="3"/>
-      <c r="B1" s="1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
+      <c r="B1" s="2"/>
       <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="1"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="2"/>
       <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="3"/>
-      <c r="J1" s="1"/>
+      <c r="H1" s="3"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="2"/>
       <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-      <c r="M1" s="3"/>
-      <c r="N1" s="1"/>
+      <c r="L1" s="3"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="2"/>
       <c r="O1" s="2"/>
-      <c r="P1" s="2"/>
-      <c r="Q1" s="3"/>
-      <c r="R1" s="1"/>
+      <c r="P1" s="3"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="2"/>
       <c r="S1" s="2"/>
-      <c r="T1" s="2"/>
-      <c r="U1" s="3"/>
-      <c r="V1" s="1"/>
+      <c r="T1" s="3"/>
+      <c r="U1" s="1"/>
+      <c r="V1" s="2"/>
       <c r="W1" s="2"/>
-      <c r="X1" s="2"/>
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
-      <c r="A2" s="3"/>
-      <c r="B2" s="4" t="s">
+      <c r="A2" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="B2" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="5"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="4" t="s">
+      <c r="C2" s="5"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="F2" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="5"/>
-      <c r="I2" s="3"/>
-      <c r="J2" s="4" t="s">
+      <c r="G2" s="5"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="K2" s="5" t="s">
+      <c r="J2" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="L2" s="5"/>
-      <c r="M2" s="3"/>
-      <c r="N2" s="4" t="s">
+      <c r="K2" s="5"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="5" t="s">
+      <c r="N2" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="P2" s="5"/>
-      <c r="Q2" s="3"/>
-      <c r="R2" s="4" t="s">
+      <c r="O2" s="5"/>
+      <c r="P2" s="3"/>
+      <c r="Q2" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="S2" s="5" t="s">
+      <c r="R2" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="T2" s="5"/>
-      <c r="U2" s="3"/>
-      <c r="V2" s="4" t="s">
+      <c r="S2" s="5"/>
+      <c r="T2" s="3"/>
+      <c r="U2" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="W2" s="5" t="s">
+      <c r="V2" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="X2" s="5"/>
+      <c r="W2" s="5"/>
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
-      <c r="A3" s="3"/>
-      <c r="B3" s="6" t="s">
+      <c r="A3" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="7">
+      <c r="B3" s="7">
         <v>11026</v>
       </c>
-      <c r="D3" s="8"/>
-      <c r="E3" s="9"/>
-      <c r="F3" s="6" t="s">
+      <c r="C3" s="8"/>
+      <c r="D3" s="9"/>
+      <c r="E3" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="G3" s="7">
+      <c r="F3" s="7">
         <v>13917</v>
       </c>
-      <c r="H3" s="8"/>
-      <c r="I3" s="9"/>
-      <c r="J3" s="6" t="s">
+      <c r="G3" s="8"/>
+      <c r="H3" s="9"/>
+      <c r="I3" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="K3" s="7">
+      <c r="J3" s="7">
         <v>9053</v>
       </c>
-      <c r="L3" s="8"/>
-      <c r="M3" s="9"/>
-      <c r="N3" s="6" t="s">
+      <c r="K3" s="8"/>
+      <c r="L3" s="9"/>
+      <c r="M3" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="O3" s="7">
+      <c r="N3" s="7">
         <v>27976</v>
       </c>
-      <c r="P3" s="8"/>
-      <c r="Q3" s="9"/>
-      <c r="R3" s="6" t="s">
+      <c r="O3" s="8"/>
+      <c r="P3" s="9"/>
+      <c r="Q3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="S3" s="7">
+      <c r="R3" s="7">
         <v>25638</v>
       </c>
-      <c r="T3" s="8"/>
-      <c r="U3" s="9"/>
-      <c r="V3" s="6" t="s">
+      <c r="S3" s="8"/>
+      <c r="T3" s="9"/>
+      <c r="U3" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="W3" s="7">
+      <c r="V3" s="7">
         <v>31579</v>
       </c>
-      <c r="X3" s="8"/>
+      <c r="W3" s="8"/>
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
-      <c r="A4" s="3"/>
-      <c r="B4" s="10" t="s">
+      <c r="A4" s="10" t="s">
         <v>10</v>
       </c>
+      <c r="B4" s="11">
+        <v>436.25</v>
+      </c>
       <c r="C4" s="11">
-        <v>436.25</v>
-      </c>
-      <c r="D4" s="11">
         <v>-694.134</v>
       </c>
-      <c r="E4" s="9"/>
-      <c r="F4" s="10" t="s">
+      <c r="D4" s="9"/>
+      <c r="E4" s="10" t="s">
         <v>10</v>
       </c>
+      <c r="F4" s="11">
+        <v>446.408</v>
+      </c>
       <c r="G4" s="11">
-        <v>446.408</v>
-      </c>
-      <c r="H4" s="11">
         <v>-693.016</v>
       </c>
-      <c r="I4" s="9"/>
-      <c r="J4" s="10" t="s">
+      <c r="H4" s="9"/>
+      <c r="I4" s="10" t="s">
         <v>10</v>
       </c>
+      <c r="J4" s="11">
+        <v>445.116</v>
+      </c>
       <c r="K4" s="11">
-        <v>445.116</v>
-      </c>
-      <c r="L4" s="11">
         <v>-691.777</v>
       </c>
-      <c r="M4" s="9"/>
-      <c r="N4" s="10" t="s">
+      <c r="L4" s="9"/>
+      <c r="M4" s="10" t="s">
         <v>10</v>
       </c>
+      <c r="N4" s="11">
+        <v>435.893</v>
+      </c>
       <c r="O4" s="11">
-        <v>435.893</v>
-      </c>
-      <c r="P4" s="11">
         <v>-700.587</v>
       </c>
-      <c r="Q4" s="9"/>
-      <c r="R4" s="10" t="s">
+      <c r="P4" s="9"/>
+      <c r="Q4" s="10" t="s">
         <v>10</v>
       </c>
+      <c r="R4" s="11">
+        <v>443.012</v>
+      </c>
       <c r="S4" s="11">
-        <v>443.012</v>
-      </c>
-      <c r="T4" s="11">
         <v>-696.511</v>
       </c>
-      <c r="U4" s="9"/>
-      <c r="V4" s="10" t="s">
+      <c r="T4" s="9"/>
+      <c r="U4" s="10" t="s">
         <v>10</v>
       </c>
+      <c r="V4" s="11">
+        <v>443.66</v>
+      </c>
       <c r="W4" s="11">
-        <v>443.66</v>
-      </c>
-      <c r="X4" s="11">
         <v>-697.608</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
-      <c r="A5" s="3"/>
-      <c r="B5" s="12" t="s">
+      <c r="A5" s="12" t="s">
         <v>11</v>
       </c>
+      <c r="B5" s="8" t="s">
+        <v>12</v>
+      </c>
       <c r="C5" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" s="9"/>
+      <c r="E5" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="F5" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="G5" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="9"/>
-      <c r="F5" s="12" t="s">
+      <c r="H5" s="9"/>
+      <c r="I5" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="G5" s="8" t="s">
+      <c r="J5" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="H5" s="8" t="s">
+      <c r="K5" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="I5" s="9"/>
-      <c r="J5" s="12" t="s">
+      <c r="L5" s="9"/>
+      <c r="M5" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="K5" s="8" t="s">
+      <c r="N5" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="L5" s="8" t="s">
+      <c r="O5" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="M5" s="9"/>
-      <c r="N5" s="12" t="s">
+      <c r="P5" s="9"/>
+      <c r="Q5" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="O5" s="8" t="s">
+      <c r="R5" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="P5" s="8" t="s">
+      <c r="S5" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="Q5" s="9"/>
-      <c r="R5" s="12" t="s">
+      <c r="T5" s="9"/>
+      <c r="U5" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="S5" s="8" t="s">
+      <c r="V5" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="T5" s="8" t="s">
+      <c r="W5" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="U5" s="9"/>
-      <c r="V5" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="W5" s="8" t="s">
-        <v>12</v>
-      </c>
-      <c r="X5" s="8" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
-      <c r="A6" s="3"/>
-      <c r="B6" s="7">
+      <c r="A6" s="7">
         <v>0</v>
       </c>
+      <c r="B6" s="11">
+        <v>2.07083</v>
+      </c>
       <c r="C6" s="11">
-        <v>2.07083</v>
-      </c>
-      <c r="D6" s="11">
         <v>-1.04691</v>
       </c>
-      <c r="E6" s="9"/>
-      <c r="F6" s="7">
+      <c r="D6" s="9"/>
+      <c r="E6" s="7">
         <v>0</v>
       </c>
+      <c r="F6" s="11">
+        <v>2.19338</v>
+      </c>
       <c r="G6" s="11">
-        <v>2.19338</v>
-      </c>
-      <c r="H6" s="11">
         <v>-1.49219</v>
       </c>
-      <c r="I6" s="9"/>
-      <c r="J6" s="7">
+      <c r="H6" s="9"/>
+      <c r="I6" s="7">
         <v>0</v>
       </c>
+      <c r="J6" s="11">
+        <v>1.98781</v>
+      </c>
       <c r="K6" s="11">
-        <v>1.98781</v>
-      </c>
-      <c r="L6" s="11">
         <v>-1.26085</v>
       </c>
-      <c r="M6" s="9"/>
-      <c r="N6" s="7">
+      <c r="L6" s="9"/>
+      <c r="M6" s="7">
         <v>0</v>
       </c>
+      <c r="N6" s="11">
+        <v>1.42966</v>
+      </c>
       <c r="O6" s="11">
-        <v>1.42966</v>
-      </c>
-      <c r="P6" s="11">
         <v>-0.49437</v>
       </c>
-      <c r="Q6" s="9"/>
-      <c r="R6" s="7">
+      <c r="P6" s="9"/>
+      <c r="Q6" s="7">
         <v>0</v>
       </c>
+      <c r="R6" s="11">
+        <v>1.46425</v>
+      </c>
       <c r="S6" s="11">
-        <v>1.46425</v>
-      </c>
-      <c r="T6" s="11">
         <v>-0.752913</v>
       </c>
-      <c r="U6" s="9"/>
-      <c r="V6" s="7">
+      <c r="T6" s="9"/>
+      <c r="U6" s="7">
         <v>0</v>
       </c>
+      <c r="V6" s="11">
+        <v>1.80376</v>
+      </c>
       <c r="W6" s="11">
-        <v>1.80376</v>
-      </c>
-      <c r="X6" s="11">
         <v>-1.11653</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
-      <c r="A7" s="3"/>
+      <c r="A7" s="11">
+        <v>0.05</v>
+      </c>
       <c r="B7" s="11">
+        <v>0.379938</v>
+      </c>
+      <c r="C7" s="11">
+        <v>-1.31601</v>
+      </c>
+      <c r="D7" s="9"/>
+      <c r="E7" s="11">
         <v>0.05</v>
       </c>
-      <c r="C7" s="11">
-        <v>0.379938</v>
-      </c>
-      <c r="D7" s="11">
-        <v>-1.31601</v>
-      </c>
-      <c r="E7" s="9"/>
       <c r="F7" s="11">
+        <v>0.397236</v>
+      </c>
+      <c r="G7" s="11">
+        <v>-1.33835</v>
+      </c>
+      <c r="H7" s="9"/>
+      <c r="I7" s="11">
         <v>0.05</v>
       </c>
-      <c r="G7" s="11">
-        <v>0.397236</v>
-      </c>
-      <c r="H7" s="11">
-        <v>-1.33835</v>
-      </c>
-      <c r="I7" s="9"/>
       <c r="J7" s="11">
+        <v>0.353105</v>
+      </c>
+      <c r="K7" s="11">
+        <v>-1.27583</v>
+      </c>
+      <c r="L7" s="9"/>
+      <c r="M7" s="11">
         <v>0.05</v>
       </c>
-      <c r="K7" s="11">
-        <v>0.353105</v>
-      </c>
-      <c r="L7" s="11">
-        <v>-1.27583</v>
-      </c>
-      <c r="M7" s="9"/>
       <c r="N7" s="11">
+        <v>-0.00118141</v>
+      </c>
+      <c r="O7" s="11">
+        <v>-0.798503</v>
+      </c>
+      <c r="P7" s="9"/>
+      <c r="Q7" s="11">
         <v>0.05</v>
       </c>
-      <c r="O7" s="11">
-        <v>-0.00118141</v>
-      </c>
-      <c r="P7" s="11">
-        <v>-0.798503</v>
-      </c>
-      <c r="Q7" s="9"/>
       <c r="R7" s="11">
+        <v>0.0353479</v>
+      </c>
+      <c r="S7" s="11">
+        <v>-0.857803</v>
+      </c>
+      <c r="T7" s="9"/>
+      <c r="U7" s="11">
         <v>0.05</v>
       </c>
-      <c r="S7" s="11">
-        <v>0.0353479</v>
-      </c>
-      <c r="T7" s="11">
-        <v>-0.857803</v>
-      </c>
-      <c r="U7" s="9"/>
       <c r="V7" s="11">
-        <v>0.05</v>
+        <v>0.10519</v>
       </c>
       <c r="W7" s="11">
-        <v>0.10519</v>
-      </c>
-      <c r="X7" s="11">
         <v>-1.04652</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
-      <c r="A8" s="3"/>
+      <c r="A8" s="11">
+        <v>0.1</v>
+      </c>
       <c r="B8" s="11">
+        <v>-0.296426</v>
+      </c>
+      <c r="C8" s="11">
+        <v>-1.42286</v>
+      </c>
+      <c r="D8" s="9"/>
+      <c r="E8" s="11">
         <v>0.1</v>
       </c>
-      <c r="C8" s="11">
-        <v>-0.296426</v>
-      </c>
-      <c r="D8" s="11">
-        <v>-1.42286</v>
-      </c>
-      <c r="E8" s="9"/>
       <c r="F8" s="11">
+        <v>-0.433053</v>
+      </c>
+      <c r="G8" s="11">
+        <v>-1.16756</v>
+      </c>
+      <c r="H8" s="9"/>
+      <c r="I8" s="11">
         <v>0.1</v>
       </c>
-      <c r="G8" s="11">
-        <v>-0.433053</v>
-      </c>
-      <c r="H8" s="11">
-        <v>-1.16756</v>
-      </c>
-      <c r="I8" s="9"/>
       <c r="J8" s="11">
+        <v>-0.143807</v>
+      </c>
+      <c r="K8" s="11">
+        <v>-1.37206</v>
+      </c>
+      <c r="L8" s="9"/>
+      <c r="M8" s="11">
         <v>0.1</v>
       </c>
-      <c r="K8" s="11">
-        <v>-0.143807</v>
-      </c>
-      <c r="L8" s="11">
-        <v>-1.37206</v>
-      </c>
-      <c r="M8" s="9"/>
       <c r="N8" s="11">
+        <v>-0.516377</v>
+      </c>
+      <c r="O8" s="11">
+        <v>-0.938442</v>
+      </c>
+      <c r="P8" s="9"/>
+      <c r="Q8" s="11">
         <v>0.1</v>
       </c>
-      <c r="O8" s="11">
-        <v>-0.516377</v>
-      </c>
-      <c r="P8" s="11">
-        <v>-0.938442</v>
-      </c>
-      <c r="Q8" s="9"/>
       <c r="R8" s="11">
+        <v>-0.303169</v>
+      </c>
+      <c r="S8" s="11">
+        <v>-1.0262</v>
+      </c>
+      <c r="T8" s="9"/>
+      <c r="U8" s="11">
         <v>0.1</v>
       </c>
-      <c r="S8" s="11">
-        <v>-0.303169</v>
-      </c>
-      <c r="T8" s="11">
-        <v>-1.0262</v>
-      </c>
-      <c r="U8" s="9"/>
       <c r="V8" s="11">
-        <v>0.1</v>
+        <v>-0.771967</v>
       </c>
       <c r="W8" s="11">
-        <v>-0.771967</v>
-      </c>
-      <c r="X8" s="11">
         <v>-0.842895</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
-      <c r="A9" s="3"/>
+      <c r="A9" s="11">
+        <v>0.15</v>
+      </c>
       <c r="B9" s="11">
+        <v>-0.588533</v>
+      </c>
+      <c r="C9" s="11">
+        <v>-1.5015</v>
+      </c>
+      <c r="D9" s="9"/>
+      <c r="E9" s="11">
         <v>0.15</v>
       </c>
-      <c r="C9" s="11">
-        <v>-0.588533</v>
-      </c>
-      <c r="D9" s="11">
-        <v>-1.5015</v>
-      </c>
-      <c r="E9" s="9"/>
       <c r="F9" s="11">
+        <v>-0.865536</v>
+      </c>
+      <c r="G9" s="11">
+        <v>-1.04943</v>
+      </c>
+      <c r="H9" s="9"/>
+      <c r="I9" s="11">
         <v>0.15</v>
       </c>
-      <c r="G9" s="11">
-        <v>-0.865536</v>
-      </c>
-      <c r="H9" s="11">
-        <v>-1.04943</v>
-      </c>
-      <c r="I9" s="9"/>
       <c r="J9" s="11">
+        <v>-0.28426</v>
+      </c>
+      <c r="K9" s="11">
+        <v>-1.45378</v>
+      </c>
+      <c r="L9" s="9"/>
+      <c r="M9" s="11">
         <v>0.15</v>
       </c>
-      <c r="K9" s="11">
-        <v>-0.28426</v>
-      </c>
-      <c r="L9" s="11">
-        <v>-1.45378</v>
-      </c>
-      <c r="M9" s="9"/>
       <c r="N9" s="11">
+        <v>-0.701271</v>
+      </c>
+      <c r="O9" s="11">
+        <v>-1.03524</v>
+      </c>
+      <c r="P9" s="9"/>
+      <c r="Q9" s="11">
         <v>0.15</v>
       </c>
-      <c r="O9" s="11">
-        <v>-0.701271</v>
-      </c>
-      <c r="P9" s="11">
-        <v>-1.03524</v>
-      </c>
-      <c r="Q9" s="9"/>
       <c r="R9" s="11">
+        <v>-0.332186</v>
+      </c>
+      <c r="S9" s="11">
+        <v>-1.14911</v>
+      </c>
+      <c r="T9" s="9"/>
+      <c r="U9" s="11">
         <v>0.15</v>
       </c>
-      <c r="S9" s="11">
-        <v>-0.332186</v>
-      </c>
-      <c r="T9" s="11">
-        <v>-1.14911</v>
-      </c>
-      <c r="U9" s="9"/>
       <c r="V9" s="11">
-        <v>0.15</v>
+        <v>-1.258</v>
       </c>
       <c r="W9" s="11">
-        <v>-1.258</v>
-      </c>
-      <c r="X9" s="11">
         <v>-0.698908</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
-      <c r="A10" s="3"/>
+      <c r="A10" s="11">
+        <v>0.2</v>
+      </c>
       <c r="B10" s="11">
+        <v>-0.676872</v>
+      </c>
+      <c r="C10" s="11">
+        <v>-1.56276</v>
+      </c>
+      <c r="D10" s="9"/>
+      <c r="E10" s="11">
         <v>0.2</v>
       </c>
-      <c r="C10" s="11">
-        <v>-0.676872</v>
-      </c>
-      <c r="D10" s="11">
-        <v>-1.56276</v>
-      </c>
-      <c r="E10" s="9"/>
       <c r="F10" s="11">
+        <v>-1.07486</v>
+      </c>
+      <c r="G10" s="11">
+        <v>-0.986102</v>
+      </c>
+      <c r="H10" s="9"/>
+      <c r="I10" s="11">
         <v>0.2</v>
       </c>
-      <c r="G10" s="11">
-        <v>-1.07486</v>
-      </c>
-      <c r="H10" s="11">
-        <v>-0.986102</v>
-      </c>
-      <c r="I10" s="9"/>
       <c r="J10" s="11">
+        <v>-0.237891</v>
+      </c>
+      <c r="K10" s="11">
+        <v>-1.5633</v>
+      </c>
+      <c r="L10" s="9"/>
+      <c r="M10" s="11">
         <v>0.2</v>
       </c>
-      <c r="K10" s="11">
-        <v>-0.237891</v>
-      </c>
-      <c r="L10" s="11">
-        <v>-1.5633</v>
-      </c>
-      <c r="M10" s="9"/>
       <c r="N10" s="11">
+        <v>-0.737125</v>
+      </c>
+      <c r="O10" s="11">
+        <v>-1.10523</v>
+      </c>
+      <c r="P10" s="9"/>
+      <c r="Q10" s="11">
         <v>0.2</v>
       </c>
-      <c r="O10" s="11">
-        <v>-0.737125</v>
-      </c>
-      <c r="P10" s="11">
-        <v>-1.10523</v>
-      </c>
-      <c r="Q10" s="9"/>
       <c r="R10" s="11">
+        <v>-0.227221</v>
+      </c>
+      <c r="S10" s="11">
+        <v>-1.27469</v>
+      </c>
+      <c r="T10" s="9"/>
+      <c r="U10" s="11">
         <v>0.2</v>
       </c>
-      <c r="S10" s="11">
-        <v>-0.227221</v>
-      </c>
-      <c r="T10" s="11">
-        <v>-1.27469</v>
-      </c>
-      <c r="U10" s="9"/>
       <c r="V10" s="11">
-        <v>0.2</v>
+        <v>-1.52838</v>
       </c>
       <c r="W10" s="11">
-        <v>-1.52838</v>
-      </c>
-      <c r="X10" s="11">
         <v>-0.599434</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
-      <c r="A11" s="3"/>
+      <c r="A11" s="11">
+        <v>0.25</v>
+      </c>
       <c r="B11" s="11">
+        <v>-0.690504</v>
+      </c>
+      <c r="C11" s="11">
+        <v>-1.57962</v>
+      </c>
+      <c r="D11" s="9"/>
+      <c r="E11" s="11">
         <v>0.25</v>
       </c>
-      <c r="C11" s="11">
-        <v>-0.690504</v>
-      </c>
-      <c r="D11" s="11">
-        <v>-1.57962</v>
-      </c>
-      <c r="E11" s="9"/>
       <c r="F11" s="11">
+        <v>-1.12209</v>
+      </c>
+      <c r="G11" s="11">
+        <v>-0.972673</v>
+      </c>
+      <c r="H11" s="9"/>
+      <c r="I11" s="11">
         <v>0.25</v>
       </c>
-      <c r="G11" s="11">
-        <v>-1.12209</v>
-      </c>
-      <c r="H11" s="11">
-        <v>-0.972673</v>
-      </c>
-      <c r="I11" s="9"/>
       <c r="J11" s="11">
+        <v>-0.214538</v>
+      </c>
+      <c r="K11" s="11">
+        <v>-1.59787</v>
+      </c>
+      <c r="L11" s="9"/>
+      <c r="M11" s="11">
         <v>0.25</v>
       </c>
-      <c r="K11" s="11">
-        <v>-0.214538</v>
-      </c>
-      <c r="L11" s="11">
-        <v>-1.59787</v>
-      </c>
-      <c r="M11" s="9"/>
       <c r="N11" s="11">
+        <v>-0.740894</v>
+      </c>
+      <c r="O11" s="11">
+        <v>-1.12382</v>
+      </c>
+      <c r="P11" s="9"/>
+      <c r="Q11" s="11">
         <v>0.25</v>
       </c>
-      <c r="O11" s="11">
-        <v>-0.740894</v>
-      </c>
-      <c r="P11" s="11">
-        <v>-1.12382</v>
-      </c>
-      <c r="Q11" s="9"/>
       <c r="R11" s="11">
+        <v>-0.191684</v>
+      </c>
+      <c r="S11" s="11">
+        <v>-1.31222</v>
+      </c>
+      <c r="T11" s="9"/>
+      <c r="U11" s="11">
         <v>0.25</v>
       </c>
-      <c r="S11" s="11">
-        <v>-0.191684</v>
-      </c>
-      <c r="T11" s="11">
-        <v>-1.31222</v>
-      </c>
-      <c r="U11" s="9"/>
       <c r="V11" s="11">
-        <v>0.25</v>
+        <v>-1.59444</v>
       </c>
       <c r="W11" s="11">
-        <v>-1.59444</v>
-      </c>
-      <c r="X11" s="11">
         <v>-0.574154</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
-      <c r="A12" s="3"/>
+      <c r="A12" s="11">
+        <v>0.30198</v>
+      </c>
       <c r="B12" s="11">
+        <v>-0.722761</v>
+      </c>
+      <c r="C12" s="11">
+        <v>-1.63129</v>
+      </c>
+      <c r="D12" s="9"/>
+      <c r="E12" s="11">
         <v>0.30198</v>
       </c>
-      <c r="C12" s="11">
-        <v>-0.722761</v>
-      </c>
-      <c r="D12" s="11">
-        <v>-1.63129</v>
-      </c>
-      <c r="E12" s="9"/>
       <c r="F12" s="11">
+        <v>-1.2493</v>
+      </c>
+      <c r="G12" s="11">
+        <v>-0.941325</v>
+      </c>
+      <c r="H12" s="9"/>
+      <c r="I12" s="11">
         <v>0.30198</v>
       </c>
-      <c r="G12" s="11">
-        <v>-1.2493</v>
-      </c>
-      <c r="H12" s="11">
-        <v>-0.941325</v>
-      </c>
-      <c r="I12" s="9"/>
       <c r="J12" s="11">
+        <v>-0.146768</v>
+      </c>
+      <c r="K12" s="11">
+        <v>-1.6994</v>
+      </c>
+      <c r="L12" s="9"/>
+      <c r="M12" s="11">
         <v>0.30198</v>
       </c>
-      <c r="K12" s="11">
-        <v>-0.146768</v>
-      </c>
-      <c r="L12" s="11">
-        <v>-1.6994</v>
-      </c>
-      <c r="M12" s="9"/>
       <c r="N12" s="11">
+        <v>-0.749206</v>
+      </c>
+      <c r="O12" s="11">
+        <v>-1.1787</v>
+      </c>
+      <c r="P12" s="9"/>
+      <c r="Q12" s="11">
         <v>0.30198</v>
       </c>
-      <c r="O12" s="11">
-        <v>-0.749206</v>
-      </c>
-      <c r="P12" s="11">
-        <v>-1.1787</v>
-      </c>
-      <c r="Q12" s="9"/>
       <c r="R12" s="11">
+        <v>-0.0922755</v>
+      </c>
+      <c r="S12" s="11">
+        <v>-1.42058</v>
+      </c>
+      <c r="T12" s="9"/>
+      <c r="U12" s="11">
         <v>0.30198</v>
       </c>
-      <c r="S12" s="11">
-        <v>-0.0922755</v>
-      </c>
-      <c r="T12" s="11">
-        <v>-1.42058</v>
-      </c>
-      <c r="U12" s="9"/>
       <c r="V12" s="11">
-        <v>0.30198</v>
+        <v>-1.77418</v>
       </c>
       <c r="W12" s="11">
-        <v>-1.77418</v>
-      </c>
-      <c r="X12" s="11">
         <v>-0.508762</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
-      <c r="A13" s="3"/>
+      <c r="A13" s="11">
+        <v>0.35365</v>
+      </c>
       <c r="B13" s="11">
+        <v>-0.743351</v>
+      </c>
+      <c r="C13" s="11">
+        <v>-1.67653</v>
+      </c>
+      <c r="D13" s="9"/>
+      <c r="E13" s="11">
         <v>0.35365</v>
       </c>
-      <c r="C13" s="11">
-        <v>-0.743351</v>
-      </c>
-      <c r="D13" s="11">
-        <v>-1.67653</v>
-      </c>
-      <c r="E13" s="9"/>
       <c r="F13" s="11">
+        <v>-1.34348</v>
+      </c>
+      <c r="G13" s="11">
+        <v>-0.922488</v>
+      </c>
+      <c r="H13" s="9"/>
+      <c r="I13" s="11">
         <v>0.35365</v>
       </c>
-      <c r="G13" s="11">
-        <v>-1.34348</v>
-      </c>
-      <c r="H13" s="11">
-        <v>-0.922488</v>
-      </c>
-      <c r="I13" s="9"/>
       <c r="J13" s="11">
+        <v>-0.0955838</v>
+      </c>
+      <c r="K13" s="11">
+        <v>-1.77811</v>
+      </c>
+      <c r="L13" s="9"/>
+      <c r="M13" s="11">
         <v>0.35365</v>
       </c>
-      <c r="K13" s="11">
-        <v>-0.0955838</v>
-      </c>
-      <c r="L13" s="11">
-        <v>-1.77811</v>
-      </c>
-      <c r="M13" s="9"/>
       <c r="N13" s="11">
+        <v>-0.753754</v>
+      </c>
+      <c r="O13" s="11">
+        <v>-1.2232</v>
+      </c>
+      <c r="P13" s="9"/>
+      <c r="Q13" s="11">
         <v>0.35365</v>
       </c>
-      <c r="O13" s="11">
-        <v>-0.753754</v>
-      </c>
-      <c r="P13" s="11">
-        <v>-1.2232</v>
-      </c>
-      <c r="Q13" s="9"/>
       <c r="R13" s="11">
+        <v>-0.0179217</v>
+      </c>
+      <c r="S13" s="11">
+        <v>-1.50348</v>
+      </c>
+      <c r="T13" s="9"/>
+      <c r="U13" s="11">
         <v>0.35365</v>
       </c>
-      <c r="S13" s="11">
-        <v>-0.0179217</v>
-      </c>
-      <c r="T13" s="11">
-        <v>-1.50348</v>
-      </c>
-      <c r="U13" s="9"/>
       <c r="V13" s="11">
-        <v>0.35365</v>
+        <v>-1.90615</v>
       </c>
       <c r="W13" s="11">
-        <v>-1.90615</v>
-      </c>
-      <c r="X13" s="11">
         <v>-0.465848</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
-      <c r="A14" s="3"/>
+      <c r="A14" s="11">
+        <v>0.40358</v>
+      </c>
       <c r="B14" s="11">
+        <v>-0.763455</v>
+      </c>
+      <c r="C14" s="11">
+        <v>-1.72872</v>
+      </c>
+      <c r="D14" s="9"/>
+      <c r="E14" s="11">
         <v>0.40358</v>
       </c>
-      <c r="C14" s="11">
-        <v>-0.763455</v>
-      </c>
-      <c r="D14" s="11">
-        <v>-1.72872</v>
-      </c>
-      <c r="E14" s="9"/>
       <c r="F14" s="11">
+        <v>-1.44278</v>
+      </c>
+      <c r="G14" s="11">
+        <v>-0.906512</v>
+      </c>
+      <c r="H14" s="9"/>
+      <c r="I14" s="11">
         <v>0.40358</v>
       </c>
-      <c r="G14" s="11">
-        <v>-1.44278</v>
-      </c>
-      <c r="H14" s="11">
-        <v>-0.906512</v>
-      </c>
-      <c r="I14" s="9"/>
       <c r="J14" s="11">
+        <v>-0.0434075</v>
+      </c>
+      <c r="K14" s="11">
+        <v>-1.86173</v>
+      </c>
+      <c r="L14" s="9"/>
+      <c r="M14" s="11">
         <v>0.40358</v>
       </c>
-      <c r="K14" s="11">
-        <v>-0.0434075</v>
-      </c>
-      <c r="L14" s="11">
-        <v>-1.86173</v>
-      </c>
-      <c r="M14" s="9"/>
       <c r="N14" s="11">
+        <v>-0.758052</v>
+      </c>
+      <c r="O14" s="11">
+        <v>-1.273</v>
+      </c>
+      <c r="P14" s="9"/>
+      <c r="Q14" s="11">
         <v>0.40358</v>
       </c>
-      <c r="O14" s="11">
-        <v>-0.758052</v>
-      </c>
-      <c r="P14" s="11">
-        <v>-1.273</v>
-      </c>
-      <c r="Q14" s="9"/>
       <c r="R14" s="11">
+        <v>0.0583407</v>
+      </c>
+      <c r="S14" s="11">
+        <v>-1.59047</v>
+      </c>
+      <c r="T14" s="9"/>
+      <c r="U14" s="11">
         <v>0.40358</v>
       </c>
-      <c r="S14" s="11">
-        <v>0.0583407</v>
-      </c>
-      <c r="T14" s="11">
-        <v>-1.59047</v>
-      </c>
-      <c r="U14" s="9"/>
       <c r="V14" s="11">
-        <v>0.40358</v>
+        <v>-2.04346</v>
       </c>
       <c r="W14" s="11">
-        <v>-2.04346</v>
-      </c>
-      <c r="X14" s="11">
         <v>-0.426493</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
-      <c r="A15" s="3"/>
+      <c r="A15" s="11">
+        <v>0.45421</v>
+      </c>
       <c r="B15" s="11">
+        <v>-0.774728</v>
+      </c>
+      <c r="C15" s="11">
+        <v>-1.77109</v>
+      </c>
+      <c r="D15" s="9"/>
+      <c r="E15" s="11">
         <v>0.45421</v>
       </c>
-      <c r="C15" s="11">
-        <v>-0.774728</v>
-      </c>
-      <c r="D15" s="11">
-        <v>-1.77109</v>
-      </c>
-      <c r="E15" s="9"/>
       <c r="F15" s="11">
+        <v>-1.51614</v>
+      </c>
+      <c r="G15" s="11">
+        <v>-0.896076</v>
+      </c>
+      <c r="H15" s="9"/>
+      <c r="I15" s="11">
         <v>0.45421</v>
       </c>
-      <c r="G15" s="11">
-        <v>-1.51614</v>
-      </c>
-      <c r="H15" s="11">
-        <v>-0.896076</v>
-      </c>
-      <c r="I15" s="9"/>
       <c r="J15" s="11">
+        <v>-0.00135608</v>
+      </c>
+      <c r="K15" s="11">
+        <v>-1.9254</v>
+      </c>
+      <c r="L15" s="9"/>
+      <c r="M15" s="11">
         <v>0.45421</v>
       </c>
-      <c r="K15" s="11">
-        <v>-0.00135608</v>
-      </c>
-      <c r="L15" s="11">
-        <v>-1.9254</v>
-      </c>
-      <c r="M15" s="9"/>
       <c r="N15" s="11">
+        <v>-0.758545</v>
+      </c>
+      <c r="O15" s="11">
+        <v>-1.31232</v>
+      </c>
+      <c r="P15" s="9"/>
+      <c r="Q15" s="11">
         <v>0.45421</v>
       </c>
-      <c r="O15" s="11">
-        <v>-0.758545</v>
-      </c>
-      <c r="P15" s="11">
-        <v>-1.31232</v>
-      </c>
-      <c r="Q15" s="9"/>
       <c r="R15" s="11">
+        <v>0.118315</v>
+      </c>
+      <c r="S15" s="11">
+        <v>-1.65694</v>
+      </c>
+      <c r="T15" s="9"/>
+      <c r="U15" s="11">
         <v>0.45421</v>
       </c>
-      <c r="S15" s="11">
-        <v>0.118315</v>
-      </c>
-      <c r="T15" s="11">
-        <v>-1.65694</v>
-      </c>
-      <c r="U15" s="9"/>
       <c r="V15" s="11">
-        <v>0.45421</v>
+        <v>-2.1454</v>
       </c>
       <c r="W15" s="11">
-        <v>-2.1454</v>
-      </c>
-      <c r="X15" s="11">
         <v>-0.398924</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
-      <c r="A16" s="3"/>
+      <c r="A16" s="11">
+        <v>0.50322</v>
+      </c>
       <c r="B16" s="11">
+        <v>-0.796713</v>
+      </c>
+      <c r="C16" s="11">
+        <v>-1.82329</v>
+      </c>
+      <c r="D16" s="9"/>
+      <c r="E16" s="11">
         <v>0.50322</v>
       </c>
-      <c r="C16" s="11">
-        <v>-0.796713</v>
-      </c>
-      <c r="D16" s="11">
-        <v>-1.82329</v>
-      </c>
-      <c r="E16" s="9"/>
       <c r="F16" s="11">
+        <v>-1.60968</v>
+      </c>
+      <c r="G16" s="11">
+        <v>-0.886316</v>
+      </c>
+      <c r="H16" s="9"/>
+      <c r="I16" s="11">
         <v>0.50322</v>
       </c>
-      <c r="G16" s="11">
-        <v>-1.60968</v>
-      </c>
-      <c r="H16" s="11">
-        <v>-0.886316</v>
-      </c>
-      <c r="I16" s="9"/>
       <c r="J16" s="11">
+        <v>0.0336862</v>
+      </c>
+      <c r="K16" s="11">
+        <v>-1.9956</v>
+      </c>
+      <c r="L16" s="9"/>
+      <c r="M16" s="11">
         <v>0.50322</v>
       </c>
-      <c r="K16" s="11">
-        <v>0.0336862</v>
-      </c>
-      <c r="L16" s="11">
-        <v>-1.9956</v>
-      </c>
-      <c r="M16" s="9"/>
       <c r="N16" s="11">
+        <v>-0.767902</v>
+      </c>
+      <c r="O16" s="11">
+        <v>-1.3604</v>
+      </c>
+      <c r="P16" s="9"/>
+      <c r="Q16" s="11">
         <v>0.50322</v>
       </c>
-      <c r="O16" s="11">
-        <v>-0.767902</v>
-      </c>
-      <c r="P16" s="11">
-        <v>-1.3604</v>
-      </c>
-      <c r="Q16" s="9"/>
       <c r="R16" s="11">
+        <v>0.174036</v>
+      </c>
+      <c r="S16" s="11">
+        <v>-1.73061</v>
+      </c>
+      <c r="T16" s="9"/>
+      <c r="U16" s="11">
         <v>0.50322</v>
       </c>
-      <c r="S16" s="11">
-        <v>0.174036</v>
-      </c>
-      <c r="T16" s="11">
-        <v>-1.73061</v>
-      </c>
-      <c r="U16" s="9"/>
       <c r="V16" s="11">
-        <v>0.50322</v>
+        <v>-2.26915</v>
       </c>
       <c r="W16" s="11">
-        <v>-2.26915</v>
-      </c>
-      <c r="X16" s="11">
         <v>-0.372319</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
-      <c r="A17" s="3"/>
+      <c r="A17" s="11">
+        <v>0.55384</v>
+      </c>
       <c r="B17" s="11">
+        <v>-0.830913</v>
+      </c>
+      <c r="C17" s="11">
+        <v>-1.88642</v>
+      </c>
+      <c r="D17" s="9"/>
+      <c r="E17" s="11">
         <v>0.55384</v>
       </c>
-      <c r="C17" s="11">
-        <v>-0.830913</v>
-      </c>
-      <c r="D17" s="11">
-        <v>-1.88642</v>
-      </c>
-      <c r="E17" s="9"/>
       <c r="F17" s="11">
+        <v>-1.72514</v>
+      </c>
+      <c r="G17" s="11">
+        <v>-0.877136</v>
+      </c>
+      <c r="H17" s="9"/>
+      <c r="I17" s="11">
         <v>0.55384</v>
       </c>
-      <c r="G17" s="11">
-        <v>-1.72514</v>
-      </c>
-      <c r="H17" s="11">
-        <v>-0.877136</v>
-      </c>
-      <c r="I17" s="9"/>
       <c r="J17" s="11">
+        <v>0.0591349</v>
+      </c>
+      <c r="K17" s="11">
+        <v>-2.07278</v>
+      </c>
+      <c r="L17" s="9"/>
+      <c r="M17" s="11">
         <v>0.55384</v>
       </c>
-      <c r="K17" s="11">
-        <v>0.0591349</v>
-      </c>
-      <c r="L17" s="11">
-        <v>-2.07278</v>
-      </c>
-      <c r="M17" s="9"/>
       <c r="N17" s="11">
+        <v>-0.788375</v>
+      </c>
+      <c r="O17" s="11">
+        <v>-1.41793</v>
+      </c>
+      <c r="P17" s="9"/>
+      <c r="Q17" s="11">
         <v>0.55384</v>
       </c>
-      <c r="O17" s="11">
-        <v>-0.788375</v>
-      </c>
-      <c r="P17" s="11">
-        <v>-1.41793</v>
-      </c>
-      <c r="Q17" s="9"/>
       <c r="R17" s="11">
+        <v>0.222694</v>
+      </c>
+      <c r="S17" s="11">
+        <v>-1.81304</v>
+      </c>
+      <c r="T17" s="9"/>
+      <c r="U17" s="11">
         <v>0.55384</v>
       </c>
-      <c r="S17" s="11">
-        <v>0.222694</v>
-      </c>
-      <c r="T17" s="11">
-        <v>-1.81304</v>
-      </c>
-      <c r="U17" s="9"/>
       <c r="V17" s="11">
-        <v>0.55384</v>
+        <v>-2.41664</v>
       </c>
       <c r="W17" s="11">
-        <v>-2.41664</v>
-      </c>
-      <c r="X17" s="11">
         <v>-0.345919</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
-      <c r="A18" s="3"/>
+      <c r="A18" s="11">
+        <v>0.60384</v>
+      </c>
       <c r="B18" s="11">
+        <v>-0.859192</v>
+      </c>
+      <c r="C18" s="11">
+        <v>-1.94468</v>
+      </c>
+      <c r="D18" s="9"/>
+      <c r="E18" s="11">
         <v>0.60384</v>
       </c>
-      <c r="C18" s="11">
-        <v>-0.859192</v>
-      </c>
-      <c r="D18" s="11">
-        <v>-1.94468</v>
-      </c>
-      <c r="E18" s="9"/>
       <c r="F18" s="11">
+        <v>-1.82609</v>
+      </c>
+      <c r="G18" s="11">
+        <v>-0.871284</v>
+      </c>
+      <c r="H18" s="9"/>
+      <c r="I18" s="11">
         <v>0.60384</v>
       </c>
-      <c r="G18" s="11">
-        <v>-1.82609</v>
-      </c>
-      <c r="H18" s="11">
-        <v>-0.871284</v>
-      </c>
-      <c r="I18" s="9"/>
       <c r="J18" s="11">
+        <v>0.0807119</v>
+      </c>
+      <c r="K18" s="11">
+        <v>-2.13992</v>
+      </c>
+      <c r="L18" s="9"/>
+      <c r="M18" s="11">
         <v>0.60384</v>
       </c>
-      <c r="K18" s="11">
-        <v>0.0807119</v>
-      </c>
-      <c r="L18" s="11">
-        <v>-2.13992</v>
-      </c>
-      <c r="M18" s="9"/>
       <c r="N18" s="11">
+        <v>-0.807076</v>
+      </c>
+      <c r="O18" s="11">
+        <v>-1.47036</v>
+      </c>
+      <c r="P18" s="9"/>
+      <c r="Q18" s="11">
         <v>0.60384</v>
       </c>
-      <c r="O18" s="11">
-        <v>-0.807076</v>
-      </c>
-      <c r="P18" s="11">
-        <v>-1.47036</v>
-      </c>
-      <c r="Q18" s="9"/>
       <c r="R18" s="11">
+        <v>0.263206</v>
+      </c>
+      <c r="S18" s="11">
+        <v>-1.88572</v>
+      </c>
+      <c r="T18" s="9"/>
+      <c r="U18" s="11">
         <v>0.60384</v>
       </c>
-      <c r="S18" s="11">
-        <v>0.263206</v>
-      </c>
-      <c r="T18" s="11">
-        <v>-1.88572</v>
-      </c>
-      <c r="U18" s="9"/>
       <c r="V18" s="11">
-        <v>0.60384</v>
+        <v>-2.54657</v>
       </c>
       <c r="W18" s="11">
-        <v>-2.54657</v>
-      </c>
-      <c r="X18" s="11">
         <v>-0.325662</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
-      <c r="A19" s="3"/>
+      <c r="A19" s="11">
+        <v>0.65565</v>
+      </c>
       <c r="B19" s="11">
+        <v>-0.89518</v>
+      </c>
+      <c r="C19" s="11">
+        <v>-2.01208</v>
+      </c>
+      <c r="D19" s="9"/>
+      <c r="E19" s="11">
         <v>0.65565</v>
       </c>
-      <c r="C19" s="11">
-        <v>-0.89518</v>
-      </c>
-      <c r="D19" s="11">
-        <v>-2.01208</v>
-      </c>
-      <c r="E19" s="9"/>
       <c r="F19" s="11">
+        <v>-1.94356</v>
+      </c>
+      <c r="G19" s="11">
+        <v>-0.866435</v>
+      </c>
+      <c r="H19" s="9"/>
+      <c r="I19" s="11">
         <v>0.65565</v>
       </c>
-      <c r="G19" s="11">
-        <v>-1.94356</v>
-      </c>
-      <c r="H19" s="11">
-        <v>-0.866435</v>
-      </c>
-      <c r="I19" s="9"/>
       <c r="J19" s="11">
+        <v>0.0965013</v>
+      </c>
+      <c r="K19" s="11">
+        <v>-2.21205</v>
+      </c>
+      <c r="L19" s="9"/>
+      <c r="M19" s="11">
         <v>0.65565</v>
       </c>
-      <c r="K19" s="11">
-        <v>0.0965013</v>
-      </c>
-      <c r="L19" s="11">
-        <v>-2.21205</v>
-      </c>
-      <c r="M19" s="9"/>
       <c r="N19" s="11">
+        <v>-0.833144</v>
+      </c>
+      <c r="O19" s="11">
+        <v>-1.53077</v>
+      </c>
+      <c r="P19" s="9"/>
+      <c r="Q19" s="11">
         <v>0.65565</v>
       </c>
-      <c r="O19" s="11">
-        <v>-0.833144</v>
-      </c>
-      <c r="P19" s="11">
-        <v>-1.53077</v>
-      </c>
-      <c r="Q19" s="9"/>
       <c r="R19" s="11">
+        <v>0.29991</v>
+      </c>
+      <c r="S19" s="11">
+        <v>-1.96462</v>
+      </c>
+      <c r="T19" s="9"/>
+      <c r="U19" s="11">
         <v>0.65565</v>
       </c>
-      <c r="S19" s="11">
-        <v>0.29991</v>
-      </c>
-      <c r="T19" s="11">
-        <v>-1.96462</v>
-      </c>
-      <c r="U19" s="9"/>
       <c r="V19" s="11">
-        <v>0.65565</v>
+        <v>-2.69541</v>
       </c>
       <c r="W19" s="11">
-        <v>-2.69541</v>
-      </c>
-      <c r="X19" s="11">
         <v>-0.306748</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
-      <c r="A20" s="3"/>
+      <c r="A20" s="11">
+        <v>0.70225</v>
+      </c>
       <c r="B20" s="11">
+        <v>-0.92845</v>
+      </c>
+      <c r="C20" s="11">
+        <v>-2.06975</v>
+      </c>
+      <c r="D20" s="9"/>
+      <c r="E20" s="11">
         <v>0.70225</v>
       </c>
-      <c r="C20" s="11">
-        <v>-0.92845</v>
-      </c>
-      <c r="D20" s="11">
-        <v>-2.06975</v>
-      </c>
-      <c r="E20" s="9"/>
       <c r="F20" s="11">
+        <v>-2.04474</v>
+      </c>
+      <c r="G20" s="11">
+        <v>-0.863632</v>
+      </c>
+      <c r="H20" s="9"/>
+      <c r="I20" s="11">
         <v>0.70225</v>
       </c>
-      <c r="G20" s="11">
-        <v>-2.04474</v>
-      </c>
-      <c r="H20" s="11">
-        <v>-0.863632</v>
-      </c>
-      <c r="I20" s="9"/>
       <c r="J20" s="11">
+        <v>0.103192</v>
+      </c>
+      <c r="K20" s="11">
+        <v>-2.26941</v>
+      </c>
+      <c r="L20" s="9"/>
+      <c r="M20" s="11">
         <v>0.70225</v>
       </c>
-      <c r="K20" s="11">
-        <v>0.103192</v>
-      </c>
-      <c r="L20" s="11">
-        <v>-2.26941</v>
-      </c>
-      <c r="M20" s="9"/>
       <c r="N20" s="11">
+        <v>-0.858239</v>
+      </c>
+      <c r="O20" s="11">
+        <v>-1.58213</v>
+      </c>
+      <c r="P20" s="9"/>
+      <c r="Q20" s="11">
         <v>0.70225</v>
       </c>
-      <c r="O20" s="11">
-        <v>-0.858239</v>
-      </c>
-      <c r="P20" s="11">
-        <v>-1.58213</v>
-      </c>
-      <c r="Q20" s="9"/>
       <c r="R20" s="11">
+        <v>0.324193</v>
+      </c>
+      <c r="S20" s="11">
+        <v>-2.02789</v>
+      </c>
+      <c r="T20" s="9"/>
+      <c r="U20" s="11">
         <v>0.70225</v>
       </c>
-      <c r="S20" s="11">
-        <v>0.324193</v>
-      </c>
-      <c r="T20" s="11">
-        <v>-2.02789</v>
-      </c>
-      <c r="U20" s="9"/>
       <c r="V20" s="11">
-        <v>0.70225</v>
+        <v>-2.82126</v>
       </c>
       <c r="W20" s="11">
-        <v>-2.82126</v>
-      </c>
-      <c r="X20" s="11">
         <v>-0.293784</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
-      <c r="A21" s="3"/>
+      <c r="A21" s="11">
+        <v>0.75206</v>
+      </c>
       <c r="B21" s="11">
+        <v>-0.963866</v>
+      </c>
+      <c r="C21" s="11">
+        <v>-2.12835</v>
+      </c>
+      <c r="D21" s="9"/>
+      <c r="E21" s="11">
         <v>0.75206</v>
       </c>
-      <c r="C21" s="11">
-        <v>-0.963866</v>
-      </c>
-      <c r="D21" s="11">
-        <v>-2.12835</v>
-      </c>
-      <c r="E21" s="9"/>
       <c r="F21" s="11">
+        <v>-2.14784</v>
+      </c>
+      <c r="G21" s="11">
+        <v>-0.861441</v>
+      </c>
+      <c r="H21" s="9"/>
+      <c r="I21" s="11">
         <v>0.75206</v>
       </c>
-      <c r="G21" s="11">
-        <v>-2.14784</v>
-      </c>
-      <c r="H21" s="11">
-        <v>-0.861441</v>
-      </c>
-      <c r="I21" s="9"/>
       <c r="J21" s="11">
+        <v>0.104568</v>
+      </c>
+      <c r="K21" s="11">
+        <v>-2.32298</v>
+      </c>
+      <c r="L21" s="9"/>
+      <c r="M21" s="11">
         <v>0.75206</v>
       </c>
-      <c r="K21" s="11">
-        <v>0.104568</v>
-      </c>
-      <c r="L21" s="11">
-        <v>-2.32298</v>
-      </c>
-      <c r="M21" s="9"/>
       <c r="N21" s="11">
+        <v>-0.886742</v>
+      </c>
+      <c r="O21" s="11">
+        <v>-1.63385</v>
+      </c>
+      <c r="P21" s="9"/>
+      <c r="Q21" s="11">
         <v>0.75206</v>
       </c>
-      <c r="O21" s="11">
-        <v>-0.886742</v>
-      </c>
-      <c r="P21" s="11">
-        <v>-1.63385</v>
-      </c>
-      <c r="Q21" s="9"/>
       <c r="R21" s="11">
+        <v>0.342299</v>
+      </c>
+      <c r="S21" s="11">
+        <v>-2.08841</v>
+      </c>
+      <c r="T21" s="9"/>
+      <c r="U21" s="11">
         <v>0.75206</v>
       </c>
-      <c r="S21" s="11">
-        <v>0.342299</v>
-      </c>
-      <c r="T21" s="11">
-        <v>-2.08841</v>
-      </c>
-      <c r="U21" s="9"/>
       <c r="V21" s="11">
-        <v>0.75206</v>
+        <v>-2.94861</v>
       </c>
       <c r="W21" s="11">
-        <v>-2.94861</v>
-      </c>
-      <c r="X21" s="11">
         <v>-0.283284</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
-      <c r="A22" s="3"/>
+      <c r="A22" s="11">
+        <v>0.80139</v>
+      </c>
       <c r="B22" s="11">
+        <v>-0.999666</v>
+      </c>
+      <c r="C22" s="11">
+        <v>-2.18743</v>
+      </c>
+      <c r="D22" s="9"/>
+      <c r="E22" s="11">
         <v>0.80139</v>
       </c>
-      <c r="C22" s="11">
-        <v>-0.999666</v>
-      </c>
-      <c r="D22" s="11">
-        <v>-2.18743</v>
-      </c>
-      <c r="E22" s="9"/>
       <c r="F22" s="11">
+        <v>-2.2507</v>
+      </c>
+      <c r="G22" s="11">
+        <v>-0.860266</v>
+      </c>
+      <c r="H22" s="9"/>
+      <c r="I22" s="11">
         <v>0.80139</v>
       </c>
-      <c r="G22" s="11">
-        <v>-2.2507</v>
-      </c>
-      <c r="H22" s="11">
-        <v>-0.860266</v>
-      </c>
-      <c r="I22" s="9"/>
       <c r="J22" s="11">
+        <v>0.102576</v>
+      </c>
+      <c r="K22" s="11">
+        <v>-2.37322</v>
+      </c>
+      <c r="L22" s="9"/>
+      <c r="M22" s="11">
         <v>0.80139</v>
       </c>
-      <c r="K22" s="11">
-        <v>0.102576</v>
-      </c>
-      <c r="L22" s="11">
-        <v>-2.37322</v>
-      </c>
-      <c r="M22" s="9"/>
       <c r="N22" s="11">
+        <v>-0.916519</v>
+      </c>
+      <c r="O22" s="11">
+        <v>-1.68539</v>
+      </c>
+      <c r="P22" s="9"/>
+      <c r="Q22" s="11">
         <v>0.80139</v>
       </c>
-      <c r="O22" s="11">
-        <v>-0.916519</v>
-      </c>
-      <c r="P22" s="11">
-        <v>-1.68539</v>
-      </c>
-      <c r="Q22" s="9"/>
       <c r="R22" s="11">
+        <v>0.356344</v>
+      </c>
+      <c r="S22" s="11">
+        <v>-2.14575</v>
+      </c>
+      <c r="T22" s="9"/>
+      <c r="U22" s="11">
         <v>0.80139</v>
       </c>
-      <c r="S22" s="11">
-        <v>0.356344</v>
-      </c>
-      <c r="T22" s="11">
-        <v>-2.14575</v>
-      </c>
-      <c r="U22" s="9"/>
       <c r="V22" s="11">
-        <v>0.80139</v>
+        <v>-3.07483</v>
       </c>
       <c r="W22" s="11">
-        <v>-3.07483</v>
-      </c>
-      <c r="X22" s="11">
         <v>-0.275312</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
-      <c r="A23" s="3"/>
+      <c r="A23" s="11">
+        <v>0.85108</v>
+      </c>
       <c r="B23" s="11">
+        <v>-1.03866</v>
+      </c>
+      <c r="C23" s="11">
+        <v>-2.24744</v>
+      </c>
+      <c r="D23" s="9"/>
+      <c r="E23" s="11">
         <v>0.85108</v>
       </c>
-      <c r="C23" s="11">
-        <v>-1.03866</v>
-      </c>
-      <c r="D23" s="11">
-        <v>-2.24744</v>
-      </c>
-      <c r="E23" s="9"/>
       <c r="F23" s="11">
+        <v>-2.35626</v>
+      </c>
+      <c r="G23" s="11">
+        <v>-0.860272</v>
+      </c>
+      <c r="H23" s="9"/>
+      <c r="I23" s="11">
         <v>0.85108</v>
       </c>
-      <c r="G23" s="11">
-        <v>-2.35626</v>
-      </c>
-      <c r="H23" s="11">
-        <v>-0.860272</v>
-      </c>
-      <c r="I23" s="9"/>
       <c r="J23" s="11">
+        <v>0.0947049</v>
+      </c>
+      <c r="K23" s="11">
+        <v>-2.42116</v>
+      </c>
+      <c r="L23" s="9"/>
+      <c r="M23" s="11">
         <v>0.85108</v>
       </c>
-      <c r="K23" s="11">
-        <v>0.0947049</v>
-      </c>
-      <c r="L23" s="11">
-        <v>-2.42116</v>
-      </c>
-      <c r="M23" s="9"/>
       <c r="N23" s="11">
+        <v>-0.949984</v>
+      </c>
+      <c r="O23" s="11">
+        <v>-1.7373</v>
+      </c>
+      <c r="P23" s="9"/>
+      <c r="Q23" s="11">
         <v>0.85108</v>
       </c>
-      <c r="O23" s="11">
-        <v>-0.949984</v>
-      </c>
-      <c r="P23" s="11">
-        <v>-1.7373</v>
-      </c>
-      <c r="Q23" s="9"/>
       <c r="R23" s="11">
+        <v>0.364162</v>
+      </c>
+      <c r="S23" s="11">
+        <v>-2.20076</v>
+      </c>
+      <c r="T23" s="9"/>
+      <c r="U23" s="11">
         <v>0.85108</v>
       </c>
-      <c r="S23" s="11">
-        <v>0.364162</v>
-      </c>
-      <c r="T23" s="11">
-        <v>-2.20076</v>
-      </c>
-      <c r="U23" s="9"/>
       <c r="V23" s="11">
-        <v>0.85108</v>
+        <v>-3.20291</v>
       </c>
       <c r="W23" s="11">
-        <v>-3.20291</v>
-      </c>
-      <c r="X23" s="11">
         <v>-0.269558</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75">
-      <c r="A24" s="3"/>
+      <c r="A24" s="11">
+        <v>0.90339</v>
+      </c>
       <c r="B24" s="11">
+        <v>-1.07547</v>
+      </c>
+      <c r="C24" s="11">
+        <v>-2.30056</v>
+      </c>
+      <c r="D24" s="9"/>
+      <c r="E24" s="11">
         <v>0.90339</v>
       </c>
-      <c r="C24" s="11">
-        <v>-1.07547</v>
-      </c>
-      <c r="D24" s="11">
-        <v>-2.30056</v>
-      </c>
-      <c r="E24" s="9"/>
       <c r="F24" s="11">
+        <v>-2.4513</v>
+      </c>
+      <c r="G24" s="11">
+        <v>-0.86076</v>
+      </c>
+      <c r="H24" s="9"/>
+      <c r="I24" s="11">
         <v>0.90339</v>
       </c>
-      <c r="G24" s="11">
-        <v>-2.4513</v>
-      </c>
-      <c r="H24" s="11">
-        <v>-0.86076</v>
-      </c>
-      <c r="I24" s="9"/>
       <c r="J24" s="11">
+        <v>0.0831887</v>
+      </c>
+      <c r="K24" s="11">
+        <v>-2.46101</v>
+      </c>
+      <c r="L24" s="9"/>
+      <c r="M24" s="11">
         <v>0.90339</v>
       </c>
-      <c r="K24" s="11">
-        <v>0.0831887</v>
-      </c>
-      <c r="L24" s="11">
-        <v>-2.46101</v>
-      </c>
-      <c r="M24" s="9"/>
       <c r="N24" s="11">
+        <v>-0.982441</v>
+      </c>
+      <c r="O24" s="11">
+        <v>-1.78314</v>
+      </c>
+      <c r="P24" s="9"/>
+      <c r="Q24" s="11">
         <v>0.90339</v>
       </c>
-      <c r="O24" s="11">
-        <v>-0.982441</v>
-      </c>
-      <c r="P24" s="11">
-        <v>-1.78314</v>
-      </c>
-      <c r="Q24" s="9"/>
       <c r="R24" s="11">
+        <v>0.365962</v>
+      </c>
+      <c r="S24" s="11">
+        <v>-2.24712</v>
+      </c>
+      <c r="T24" s="9"/>
+      <c r="U24" s="11">
         <v>0.90339</v>
       </c>
-      <c r="S24" s="11">
-        <v>0.365962</v>
-      </c>
-      <c r="T24" s="11">
-        <v>-2.24712</v>
-      </c>
-      <c r="U24" s="9"/>
       <c r="V24" s="11">
-        <v>0.90339</v>
+        <v>-3.31715</v>
       </c>
       <c r="W24" s="11">
-        <v>-3.31715</v>
-      </c>
-      <c r="X24" s="11">
         <v>-0.266069</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
-      <c r="A25" s="3"/>
+      <c r="A25" s="11">
+        <v>0.95085</v>
+      </c>
       <c r="B25" s="11">
+        <v>-1.13611</v>
+      </c>
+      <c r="C25" s="11">
+        <v>-2.38697</v>
+      </c>
+      <c r="D25" s="9"/>
+      <c r="E25" s="11">
         <v>0.95085</v>
       </c>
-      <c r="C25" s="11">
-        <v>-1.13611</v>
-      </c>
-      <c r="D25" s="11">
-        <v>-2.38697</v>
-      </c>
-      <c r="E25" s="9"/>
       <c r="F25" s="11">
+        <v>-2.60601</v>
+      </c>
+      <c r="G25" s="11">
+        <v>-0.862322</v>
+      </c>
+      <c r="H25" s="9"/>
+      <c r="I25" s="11">
         <v>0.95085</v>
       </c>
-      <c r="G25" s="11">
-        <v>-2.60601</v>
-      </c>
-      <c r="H25" s="11">
-        <v>-0.862322</v>
-      </c>
-      <c r="I25" s="9"/>
       <c r="J25" s="11">
+        <v>0.0598253</v>
+      </c>
+      <c r="K25" s="11">
+        <v>-2.52092</v>
+      </c>
+      <c r="L25" s="9"/>
+      <c r="M25" s="11">
         <v>0.95085</v>
       </c>
-      <c r="K25" s="11">
-        <v>0.0598253</v>
-      </c>
-      <c r="L25" s="11">
-        <v>-2.52092</v>
-      </c>
-      <c r="M25" s="9"/>
       <c r="N25" s="11">
+        <v>-1.03744</v>
+      </c>
+      <c r="O25" s="11">
+        <v>-1.85712</v>
+      </c>
+      <c r="P25" s="9"/>
+      <c r="Q25" s="11">
         <v>0.95085</v>
       </c>
-      <c r="O25" s="11">
-        <v>-1.03744</v>
-      </c>
-      <c r="P25" s="11">
-        <v>-1.85712</v>
-      </c>
-      <c r="Q25" s="9"/>
       <c r="R25" s="11">
+        <v>0.363304</v>
+      </c>
+      <c r="S25" s="11">
+        <v>-2.31829</v>
+      </c>
+      <c r="T25" s="9"/>
+      <c r="U25" s="11">
         <v>0.95085</v>
       </c>
-      <c r="S25" s="11">
-        <v>0.363304</v>
-      </c>
-      <c r="T25" s="11">
-        <v>-2.31829</v>
-      </c>
-      <c r="U25" s="9"/>
       <c r="V25" s="11">
-        <v>0.95085</v>
+        <v>-3.50269</v>
       </c>
       <c r="W25" s="11">
-        <v>-3.50269</v>
-      </c>
-      <c r="X25" s="11">
         <v>-0.262878</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
-      <c r="A26" s="3"/>
-      <c r="B26" s="7">
+      <c r="A26" s="7">
         <v>1</v>
       </c>
+      <c r="B26" s="11">
+        <v>-1.1497</v>
+      </c>
       <c r="C26" s="11">
-        <v>-1.1497</v>
-      </c>
-      <c r="D26" s="11">
         <v>-2.40675</v>
       </c>
-      <c r="E26" s="9"/>
-      <c r="F26" s="7">
+      <c r="D26" s="9"/>
+      <c r="E26" s="7">
         <v>1</v>
       </c>
+      <c r="F26" s="11">
+        <v>-2.64118</v>
+      </c>
       <c r="G26" s="11">
-        <v>-2.64118</v>
-      </c>
-      <c r="H26" s="11">
         <v>-0.862845</v>
       </c>
-      <c r="I26" s="9"/>
-      <c r="J26" s="7">
+      <c r="H26" s="9"/>
+      <c r="I26" s="7">
         <v>1</v>
       </c>
+      <c r="J26" s="11">
+        <v>0.0542779</v>
+      </c>
       <c r="K26" s="11">
-        <v>0.0542779</v>
-      </c>
-      <c r="L26" s="11">
         <v>-2.53403</v>
       </c>
-      <c r="M26" s="9"/>
-      <c r="N26" s="7">
+      <c r="L26" s="9"/>
+      <c r="M26" s="7">
         <v>1</v>
       </c>
+      <c r="N26" s="11">
+        <v>-1.05041</v>
+      </c>
       <c r="O26" s="11">
-        <v>-1.05041</v>
-      </c>
-      <c r="P26" s="11">
         <v>-1.87418</v>
       </c>
-      <c r="Q26" s="9"/>
-      <c r="R26" s="7">
+      <c r="P26" s="9"/>
+      <c r="Q26" s="7">
         <v>1</v>
       </c>
+      <c r="R26" s="11">
+        <v>0.36188</v>
+      </c>
       <c r="S26" s="11">
-        <v>0.36188</v>
-      </c>
-      <c r="T26" s="11">
         <v>-2.33425</v>
       </c>
-      <c r="U26" s="9"/>
-      <c r="V26" s="7">
+      <c r="T26" s="9"/>
+      <c r="U26" s="7">
         <v>1</v>
       </c>
+      <c r="V26" s="11">
+        <v>-3.54533</v>
+      </c>
       <c r="W26" s="11">
-        <v>-3.54533</v>
-      </c>
-      <c r="X26" s="11">
         <v>-0.262572</v>
       </c>
     </row>
